--- a/STARTS/START2.xlsx
+++ b/STARTS/START2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="495" windowWidth="25605" windowHeight="14115" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -454,278 +454,198 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="28" customHeight="1"/>
+  <dimension ref="A1:AK3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="27.95" customHeight="1"/>
   <cols>
-    <col width="65.1640625" customWidth="1" style="2" min="1" max="1"/>
-    <col width="54.6640625" customWidth="1" style="2" min="2" max="2"/>
-    <col width="73.5" customWidth="1" style="2" min="3" max="3"/>
-    <col width="25.6640625" customWidth="1" style="2" min="4" max="4"/>
-    <col width="8.83203125" customWidth="1" style="2" min="5" max="8"/>
-    <col width="8.83203125" customWidth="1" style="2" min="9" max="16384"/>
+    <col width="65.140625" customWidth="1" style="2" min="1" max="1"/>
+    <col width="54.5703125" customWidth="1" style="2" min="2" max="2"/>
+    <col width="73.42578125" customWidth="1" style="2" min="3" max="3"/>
+    <col width="25.5703125" customWidth="1" style="2" min="4" max="4"/>
+    <col width="8.85546875" customWidth="1" style="2" min="5" max="10"/>
+    <col width="8.85546875" customWidth="1" style="2" min="11" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>used</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>used_at</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>used_project</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>used</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>used_at</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>used_project</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>used.1</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>used_at.1</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>used_project.1</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Column_8</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Column_9</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Column_10</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Column_11</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Column_12</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Column_13</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Column_14</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Column_15</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Column_16</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Column_8.1</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Column_9.1</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Column_10.1</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Column_11.1</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Column_12.1</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Column_13.1</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Column_14.1</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Column_15.1</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Column_16.1</t>
+        </is>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="3" t="n"/>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
+    <row r="2" ht="27.95" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Classic Vegetable Stir Fry</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:07:32</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>New site (p05)</t>
+        </is>
+      </c>
     </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="3" t="n"/>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="3" t="n"/>
-      <c r="B4" s="3" t="n"/>
-      <c r="C4" s="3" t="n"/>
-      <c r="D4" s="3" t="n"/>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="A5" s="3" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="A6" s="3" t="n"/>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-    </row>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="3" t="n"/>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="3" t="n"/>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="n"/>
-      <c r="D8" s="3" t="n"/>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="3" t="n"/>
-      <c r="B9" s="3" t="n"/>
-      <c r="C9" s="3" t="n"/>
-      <c r="D9" s="3" t="n"/>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="3" t="n"/>
-      <c r="B10" s="3" t="n"/>
-      <c r="C10" s="3" t="n"/>
-      <c r="D10" s="3" t="n"/>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="3" t="n"/>
-      <c r="B11" s="3" t="n"/>
-      <c r="C11" s="3" t="n"/>
-      <c r="D11" s="3" t="n"/>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="3" t="n"/>
-      <c r="B12" s="3" t="n"/>
-      <c r="C12" s="3" t="n"/>
-      <c r="D12" s="3" t="n"/>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="3" t="n"/>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="3" t="n"/>
-      <c r="B14" s="3" t="n"/>
-      <c r="C14" s="3" t="n"/>
-      <c r="D14" s="3" t="n"/>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="3" t="n"/>
-      <c r="B15" s="3" t="n"/>
-      <c r="C15" s="3" t="n"/>
-      <c r="D15" s="3" t="n"/>
-    </row>
-    <row r="16" ht="28" customHeight="1">
-      <c r="A16" s="3" t="n"/>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-      <c r="D16" s="3" t="n"/>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="3" t="n"/>
-      <c r="B17" s="3" t="n"/>
-      <c r="C17" s="3" t="n"/>
-      <c r="D17" s="3" t="n"/>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="3" t="n"/>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n"/>
-      <c r="D18" s="3" t="n"/>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="3" t="n"/>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="3" t="n"/>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n"/>
-      <c r="D20" s="3" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="3" t="n"/>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n"/>
-      <c r="D21" s="3" t="n"/>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="3" t="n"/>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
-    </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="3" t="n"/>
-      <c r="B23" s="3" t="n"/>
-      <c r="C23" s="3" t="n"/>
-      <c r="D23" s="3" t="n"/>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="3" t="n"/>
-      <c r="B24" s="3" t="n"/>
-      <c r="C24" s="3" t="n"/>
-      <c r="D24" s="3" t="n"/>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="3" t="n"/>
-      <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n"/>
-      <c r="D25" s="3" t="n"/>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="3" t="n"/>
-      <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n"/>
-      <c r="D26" s="3" t="n"/>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="3" t="n"/>
-      <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n"/>
-      <c r="D27" s="3" t="n"/>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="3" t="n"/>
-      <c r="B28" s="3" t="n"/>
-      <c r="C28" s="3" t="n"/>
-      <c r="D28" s="3" t="n"/>
-    </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="3" t="n"/>
-      <c r="B29" s="3" t="n"/>
-      <c r="C29" s="3" t="n"/>
-      <c r="D29" s="3" t="n"/>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="3" t="n"/>
-      <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="3" t="n"/>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="3" t="n"/>
-    </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="3" t="n"/>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="3" t="n"/>
-    </row>
-    <row r="35" ht="28" customHeight="1">
-      <c r="A35" s="3" t="n"/>
-    </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="3" t="n"/>
-    </row>
-    <row r="37" ht="28" customHeight="1">
-      <c r="A37" s="3" t="n"/>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="3" t="n"/>
-    </row>
-    <row r="39" ht="28" customHeight="1">
-      <c r="A39" s="3" t="n"/>
-    </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="3" t="n"/>
-    </row>
-    <row r="41" ht="28" customHeight="1">
-      <c r="A41" s="3" t="n"/>
-    </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="3" t="n"/>
-    </row>
-    <row r="43" ht="28" customHeight="1">
-      <c r="A43" s="3" t="n"/>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="3" t="n"/>
-    </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="3" t="n"/>
-    </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="3" t="n"/>
-    </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="3" t="n"/>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="3" t="n"/>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="3" t="n"/>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="3" t="n"/>
-    </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="3" t="n"/>
-    </row>
-    <row r="52" ht="28" customHeight="1">
-      <c r="A52" s="3" t="n"/>
-    </row>
-    <row r="53" ht="28" customHeight="1">
-      <c r="A53" s="3" t="n"/>
-    </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="3" t="n"/>
-    </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="3" t="n"/>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="3" t="n"/>
+    <row r="3" ht="27.95" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Chocolate Banana Pancakes</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-29 15:07:34</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>New site (p06)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
